--- a/comparison_results.xlsx
+++ b/comparison_results.xlsx
@@ -509,14 +509,14 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2609</v>
+        <v>0.2462</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>N/A (9 buildings / 7 classes — too few)</t>
+          <t>N/A (9 buildings / 3 classes)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -526,12 +526,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>0.0806</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0.0806</t>
         </is>
       </c>
     </row>
@@ -546,32 +546,32 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.1408</v>
+        <v>0.1249</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.6667</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0823</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>0.9338</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -586,32 +586,32 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.1555</v>
+        <v>0.0871</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0.1487</t>
+          <t>0.0345</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0.6799</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0.2269</t>
+          <t>0.6515</t>
         </is>
       </c>
     </row>
@@ -626,32 +626,32 @@
         <v>17</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1332</v>
+        <v>0.1893</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0.0834</t>
+          <t>0.0801</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0.7762</t>
+          <t>0.1055</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0.0857</t>
+          <t>0.6422</t>
         </is>
       </c>
     </row>
@@ -666,32 +666,32 @@
         <v>19</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.1418</v>
+        <v>0.1533</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0.4444</t>
+          <t>0.7778</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0.1231</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0.8187</t>
+          <t>0.1853</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.8936</t>
         </is>
       </c>
     </row>
@@ -706,32 +706,32 @@
         <v>21</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.2806</v>
+        <v>0.1615</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0.4545</t>
+          <t>0.7273</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.1012</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0.7409</t>
+          <t>0.1419</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0.2318</t>
+          <t>0.8521</t>
         </is>
       </c>
     </row>
@@ -749,29 +749,29 @@
         <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1567</v>
+        <v>0.1699</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0.6154</t>
+          <t>0.3846</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0.1141</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0.8784</t>
+          <t>0.1188</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0.1158</t>
+          <t>0.699</t>
         </is>
       </c>
     </row>
@@ -786,32 +786,32 @@
         <v>26</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1644</v>
+        <v>0.2014</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0.6667</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0.1126</t>
+          <t>0.1541</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0.9184</t>
+          <t>0.1391</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0.1112</t>
+          <t>0.7959</t>
         </is>
       </c>
     </row>
@@ -829,29 +829,29 @@
         <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1561</v>
+        <v>0.1773</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0.5294</t>
+          <t>0.8235</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0.2021</t>
+          <t>0.1501</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0.8687</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0.2212</t>
+          <t>0.9329</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
         <v>29</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.1924</v>
+        <v>0.243</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0.5556</t>
+          <t>0.9444</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0.2329</t>
+          <t>0.2472</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0.9075</t>
+          <t>0.228</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.9647</t>
         </is>
       </c>
     </row>
